--- a/data/review/gold_B.xlsx
+++ b/data/review/gold_B.xlsx
@@ -712,7 +712,10 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 33/2020/TT-BTTTT Sửa đổi, bổ sung một số điều của Thông tư số 08/2013/TT-BTTTT ngày 26 tháng 3 năm 2013 của Bộ trưởng Bộ Thông t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144754) | sửa đổi, bổ sung: Thông tư 21/2026/TT-BKHCN Sửa đổi, bổ sung một số điều của các Thông tư để phân cấp, cắt giảm, đơn giản hóa thủ tục hành chính trong lĩnh vự (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9272eab0-5d69-11f1-9ad3-0b0a88b57d09)</t>
+          <t>• 33/2020/TT-BTTTT — sửa đổi, bổ sung — hiệu lực 15/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144754
+• Thông tư 21/2026/TT-BKHCN Sửa đổi, bổ sung một số điều của các Thông tư để phân cấp, cắt g — sửa đổi, bổ sung — hiệu lực 20/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9272eab0-5d69-11f1-9ad3-0b0a88b57d09</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr"/>
@@ -754,7 +757,8 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 88/2025/NĐ-CP Quy định chi tiết và hướng dẫn một số điều của Nghị quyết số 193/2025/QH15 ngày 19 tháng 02 năm 2025 của Quốc hội (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177799)</t>
+          <t>• 88/2025/NĐ-CP — bãi bỏ — hiệu lực 13/04/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177799</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr"/>
@@ -796,7 +800,8 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư 21/2026/TT-BKHCN Sửa đổi, bổ sung một số điều của các Thông tư để phân cấp, cắt giảm, đơn giản hóa thủ tục hành chính trong lĩnh vự (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9272eab0-5d69-11f1-9ad3-0b0a88b57d09)</t>
+          <t>• Thông tư 21/2026/TT-BKHCN Sửa đổi, bổ sung một số điều của các Thông tư để phân cấp, cắt g — sửa đổi, bổ sung — hiệu lực 20/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9272eab0-5d69-11f1-9ad3-0b0a88b57d09</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
@@ -838,7 +843,14 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 02/VBHN-BKHCN Quy định về xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường, chất lượng sản phẩm, hàng hóa (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195) | sửa đổi, bổ sung: Nghị định số 126/2021/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công ng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199) | sửa đổi, bổ sung: Nghị định số 42/2019/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367) | sửa đổi, bổ sung: Nghị định số 106/2025/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735)</t>
+          <t>• 42/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 05/07/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367
+• 126/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199
+• 106/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735
+• 02/VBHN-BKHCN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
@@ -880,7 +892,10 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 10/VBHN-BTC Hướng dẫn việc chuyển giao quyền đại diện chủ sở hữu nhà nước tại Tổng công ty Đầu tư và Kinh doanh vốn Nhà  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157328) | sửa đổi, bổ sung: Thông tư số 119/2021/TT-BTC Sửa đổi, bổ sung một số Điều của Thông tư số 83/2018/TT-BTC ngày 30 tháng 08 năm 2018 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152520)</t>
+          <t>• 119/2021/TT-BTC — sửa đổi, bổ sung — hiệu lực 15/02/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152520
+• 10/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=157328</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
@@ -922,7 +937,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Luật Kinh doanh bảo hiểm số 08/2022/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163515) | sửa đổi, bổ sung: Luật Sửa đổi, bổ sung một số điều của Luật Kinh doanh bảo hiểm số 61/2010/QH12 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26357) | sửa đổi, bổ sung: Luật sửa đổi, bổ sung một số điều của Luật kinh doanh bảo hiểm, Luật sở hữu trí tuệ số 42/2019/QH14 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136041) | thay thế: Luật Kinh doanh bảo hiểm số 08/2022/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163515)</t>
+          <t>• Luật Sửa đổi, bổ sung một số điều của Luật Kinh doanh bảo hiểm số 61/2010/QH12 — sửa đổi, bổ sung — hiệu lực 01/07/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26357
+• Luật sửa đổi, bổ sung một số điều của Luật kinh doanh bảo hiểm, Luật sở hữu trí tuệ số 42/ — sửa đổi, bổ sung — hiệu lực 01/11/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136041
+• 08/2022/QH15 — bãi bỏ, thay thế — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163515</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
@@ -964,7 +984,22 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 86/2016/NĐ-CP Quy định điều kiện đầu tư, kinh doanh chứng khoán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112026) | hợp nhất: Văn bản hợp nhất số 20/VBHN-BTC Quy định chi tiết và hướng dẫn thỉ hành một số điều của Luật chứng khoán và Luật sửa đổi, bổ sung một số điề (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111479) | hợp nhất: Văn bản hợp nhất số 20/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều của Luật chứng khoán và Luật sửa đổi, bổ sung một số điề (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=78018) | hợp nhất: Văn bản hợp nhất số 36/VBHN-BTC Nghị định quy định chi tiết và hướng dẫn thi hành một số điều của Luật chứng khoán và Luật sửa đổi, bổ sung  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137057) | sửa đổi, bổ sung: Thông tư số 87/2017/TT-BTC Quy định chỉ tiêu an toàn tài chính và biện pháp xử lý đối vói tổ chức kỉnh doanh chửng khoán không đáp ứng chỉ t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127189) | sửa đổi, bổ sung: Nghị định số 151/2018/NĐ-CP Sửa đổi, bổ sung một số Nghị định quy định về điều kiện đầu tư, kinh doanh thuộc phạm vi quản lý nhà nước của Bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132174) | sửa đổi, bổ sung: Nghị định số 60/2015/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 58/2012/NĐ-CP ngày 20 tháng 7 năm 2012 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=68065) | thay thế: Nghị định số 155/2020/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Chứng khoán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146467)</t>
+          <t>• 60/2015/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/09/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=68065
+• 86/2016/NĐ-CP — bãi bỏ — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112026
+• 87/2017/TT-BTC — sửa đổi, bổ sung — hiệu lực 10/10/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127189
+• 151/2018/NĐ-CP — sửa đổi, bổ sung — hiệu lực 07/11/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132174
+• 155/2020/NĐ-CP — thay thế — hiệu lực 01/01/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146467
+• 20/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111479
+• 20/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=78018
+• 36/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137057</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -1006,7 +1041,12 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 29/2021/TT-BGTVT Quy định chi tiết về quản lý, khai thác cảng hàng không, sân bay (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151418) | sửa đổi, bổ sung: Thông tư số 30/2020/TT-BGTVT Sửa đổi, bổ sung một số điều Thông tư số 17/2016/TT-BGTVT ngày 30 tháng 6 năm 2016 của Bộ trưởng Bộ Giao thông  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145840) | sửa đổi, bổ sung: Thông tư số 51/2018/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 17/2016/TT-BGTVT ngày 30 tháng 6 năm 2016 của Bộ Giao thông vận tả (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132190)</t>
+          <t>• 51/2018/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 05/11/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132190
+• 30/2020/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/01/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145840
+• 29/2021/TT-BGTVT — bãi bỏ — hiệu lực 15/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151418</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
@@ -1048,7 +1088,20 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 12/2018/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 22/2014/TT-NHNN ngày 15 tháng 8 năm 2014 của Ngân hàng Nhà nước Việ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128740) | hợp nhất: Văn bản hợp nhất số 10/VBHN-NHNN Huớng dẫn thực hiện chính sách tín dụng theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128898) | hợp nhất: Văn bản hợp nhất số 09/VBHN-NHNN Hướng dẫn thực hiện chính sách tín dụng theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119977) | hợp nhất: Văn bản hợp nhất số 37/VBHN-NHNN Hướng dẫn thực hiện chính sách tín dụng theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=581081f0-4f79-11f1-a49b-efc704089ab1) | hợp nhất: Văn bản hợp nhất số 09/VBHN-NHNN Hướng dẫn thực hiện chính sách tín dụng theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=93927) | sửa đổi, bổ sung: Thông tư số 12/2018/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 22/2014/TT-NHNN ngày 15 tháng 8 năm 2014 của Ngân hàng Nhà nước Việ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128740) | sửa đổi, bổ sung: Thông tư số 85/2025/TT-NHNN Sửa đổi, bổ sung một số thông tư của Thống đốc Ngân hàng Nhà nước Việt Nam quy định về nghiệp vụ thư tín dụng và (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186599) | sửa đổi, bổ sung: Thông tư số 21/2015/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 22/2014/TT-NHNN ngày 15 tháng 8 năm 2014 của Ngân hàng Nhà nước Việ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92849)</t>
+          <t>• 21/2015/TT-NHNN — sửa đổi, bổ sung — hiệu lực 25/11/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92849
+• 12/2018/TT-NHNN — bãi bỏ, sửa đổi, bổ sung — hiệu lực 27/04/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128740
+• 85/2025/TT-NHNN — sửa đổi, bổ sung — hiệu lực 31/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186599
+• 09/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119977
+• 09/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=93927
+• 10/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128898
+• 37/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=581081f0-4f79-11f1-a49b-efc704089ab1</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -1090,7 +1143,10 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 36/2025/TT-BTC Sửa đổi, bổ sung một số điều tại các Thông tư của Bộ trưởng Bộ Tài chính trong lĩnh vực quản lý, sử dụng tài sản  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178471) | sửa đổi, bổ sung: Thông tư số 57/2018/TT-BTC Hướng dẫn thực hiện một số điều của Nghị định số 29/2018/NĐ-CP ngày 05/3/2018 của Chính phủ quy định trình tự, th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136475)</t>
+          <t>• 57/2018/TT-BTC — sửa đổi, bổ sung — hiệu lực 20/08/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136475
+• 36/2025/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178471</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
@@ -1132,7 +1188,14 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 09/VBHN-BTC Thông tư quy định về phí, lệ phí hàng hải và biểu mức thu phí, lệ phí hàng hải (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140516) | hợp nhất: Văn bản hợp nhất số 18/VBHN-BTC Quy định về phí, lệ phí hàng hải và biểm mức thu phí, lệ phí hàng hải (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152560) | sửa đổi, bổ sung: Thông tư số 74/2021/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 261/2016/TT-BTC ngày 14 tháng 11 năm 2016 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151081) | sửa đổi, bổ sung: Thông tư số 90/2019/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 261/2016/TT-BTC ngày 14 tháng 11 năm 2016 của Bô trưởng Bô Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140489)</t>
+          <t>• 90/2019/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/03/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140489
+• 74/2021/TT-BTC — sửa đổi, bổ sung — hiệu lực 12/10/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151081
+• 09/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=140516
+• 18/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152560</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
@@ -1174,7 +1237,10 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 09/2025/TT-BXD Sửa đổi, bổ sung một số điều của các Thông tư thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng liên quan đến sắp x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178499) | sửa đổi, bổ sung: Thông tư số 33/2022/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 39/2019/TT-BGTVT ngày 15 tháng 10 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158121)</t>
+          <t>• 33/2022/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/02/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158121
+• 09/2025/TT-BXD — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178499</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr"/>
@@ -1216,7 +1282,10 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 03/VBHN-BTC Hướng dẫn về phí và lệ phí thuộc thẩm quyền quyết định của Hội đồng nhân dân tỉnh, thành phố trực thuộc trun (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156563) | sửa đổi, bổ sung: Thông tư số 106/2021/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 85/2019/TT-BTC ngày 29 tháng 11 năm 2019 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152278)</t>
+          <t>• 106/2021/TT-BTC — sửa đổi, bổ sung — hiệu lực 10/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152278
+• 03/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156563</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
@@ -1258,7 +1327,12 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 34/2025/TT-BXD Quy định về quản lý, khai thác kết cấu hạ tầng đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185678) | hợp nhất: Văn bản hợp nhất số 12/VBHN-BXD Quy định về đường ngang và cấp giấy phép xây dựng công trình thiết yếu trong phạm vi đất dành cho đường sắt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182311) | sửa đổi, bổ sung: Thông tư số 09/2025/TT-BXD Sửa đổi, bổ sung một số điều của các Thông tư thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng liên quan đến sắp x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178499)</t>
+          <t>• 09/2025/TT-BXD — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178499
+• 34/2025/TT-BXD — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185678
+• 12/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182311</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
@@ -1300,7 +1374,22 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 92/2023/NĐ-CP Bãi bỏ một số văn bản quy phạm pháp luật của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308) | hợp nhất: Văn bản hợp nhất số 951/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587) | hợp nhất: Văn bản hợp nhất số 275/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653) | sửa đổi, bổ sung: Nghị định số 24/2019/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 19/2011/NĐ-CP ngày 21 tháng 3 năm 2011 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536) | sửa đổi, bổ sung: Nghị định số 18/2026/NĐ-CP Sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582) | sửa đổi, bổ sung: Nghị định số 06/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313) | sửa đổi, bổ sung: Nghị định số 114/2016/NĐ-CP Quy định lệ phí đăng ký nuôi con nuôi, lệ phí cấp giấy phép hoạt động của tổ chức con nuôi nước ngoài (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 114/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160
+• 24/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 25/04/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536
+• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 92/2023/NĐ-CP — bãi bỏ — hiệu lực 19/12/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308
+• 06/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 08/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313
+• 18/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582
+• 275/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653
+• 951/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
@@ -1342,7 +1431,20 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 01/VBHN-NHNN Hướng dẫn việc mở và sử dụng tài khoản thanh toán tại tổ chức cung ứng dịch vụ thanh toán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117474) | hợp nhất: Văn bản hợp nhất số 08/VBHN-NHNN hướng dẫn việc mở và sử dụng tài khoản thanh toán tại tổ chức cung ứng dịch vụ thanh toán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128047) | hợp nhất: Văn bản hợp nhất số 15/VBHN-NHNN Hướng dẫn việc mở và sử dụng tài khoản thanh toán tại tổ chức cung ứng dịch vụ thanh toán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145735) | hợp nhất: Văn bản hợp nhất số 13/VBHN-NHNN Hướng dẫn việc mở và sử dụng tài khoản thanh toán tại tổ chức cung ứng dịch vụ thanh toán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134441) | sửa đổi, bổ sung: Thông tư số 02/2019/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 23/2014/TT-NHNN ngày 19/8/2014 của Ngân hàng Nhà nước Việt Nam hướn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134325) | sửa đổi, bổ sung: Thông tư số 16/2020/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 23/2014/TT-NHNN ngày 19 tháng 8 năm 2014 của Thống đốc Ngân hàng Nh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145179) | sửa đổi, bổ sung: Thông tư số 32/2016/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 23/2014/TT-NHHN ngày 19/8/2014 của Ngân hàng Nhà nước Việt Nam hướn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117004)</t>
+          <t>• 32/2016/TT-NHNN — sửa đổi, bổ sung — hiệu lực 01/03/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117004
+• 02/2019/TT-NHNN — sửa đổi, bổ sung — hiệu lực 01/03/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134325
+• 16/2020/TT-NHNN — sửa đổi, bổ sung — hiệu lực 05/03/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145179
+• 01/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117474
+• 08/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128047
+• 13/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134441
+• 15/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145735</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
@@ -1384,7 +1486,18 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 17/VBHN-BNNPTNT Quy định chi tiết thi hành một số điều của Luật Lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166617) | hợp nhất: Văn bản hợp nhất số 24/VBHN-BNNPTNT Quy định chi tiết thi hành một số điều của Luật Lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172573) | sửa đổi, bổ sung: Nghị định số 183/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179099) | sửa đổi, bổ sung: Nghị định số 91/2024/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định chi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168695) | sửa đổi, bổ sung: Nghị định số 227/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289) | thay thế: Nghị định số 58/2024/NĐ-CP Một số chính sách đầu tư trong lâm nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167508) | thay thế: Nghị định số 227/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2018/NĐ-CP ngày 16 tháng 11 năm 2018 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289)</t>
+          <t>• 58/2024/NĐ-CP — thay thế — hiệu lực 15/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167508
+• 91/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 18/07/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168695
+• 183/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/08/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179099
+• 227/2025/NĐ-CP — sửa đổi, bổ sung, thay thế — hiệu lực 16/08/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186289
+• 17/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166617
+• 24/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172573</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
@@ -1426,7 +1539,16 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 35/VBHN-NHNN Quy định về cho vay hỗ trợ nhà ở theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=663a2d60-4f76-11f1-93a2-fbdcca1e0254) | hợp nhất: Văn bản hợp nhất số 44/VBHN-NHNN Quy định về cho vay hỗ trợ nhà ở theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117357) | sửa đổi, bổ sung: Thông tư số 32/2014/TT-NHNN Sửa đổi, bổ sung một số điều tại Thông tư số 11/2013/TT-NHNN ngày 15 tháng 5 năm 2013 quy định về cho vay hỗ trợ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=38262) | sửa đổi, bổ sung: Thông tư số 25/2016/TT_NHNN Sửa đổi, bổ sung một số điều tại Thông tư số 11/2013/TT-NHNN ngày 15 tháng 5 năm 2013 của Thống đốc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112570) | sửa đổi, bổ sung: Thông tư số 85/2025/TT-NHNN Sửa đổi, bổ sung một số thông tư của Thống đốc Ngân hàng Nhà nước Việt Nam quy định về nghiệp vụ thư tín dụng và (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186599)</t>
+          <t>• 32/2014/TT-NHNN — sửa đổi, bổ sung — hiệu lực 25/11/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=38262
+• 25/2016/TT_NHNN — sửa đổi, bổ sung — hiệu lực 01/08/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112570
+• 85/2025/TT-NHNN — sửa đổi, bổ sung — hiệu lực 31/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186599
+• 35/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=663a2d60-4f76-11f1-93a2-fbdcca1e0254
+• 44/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=117357</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
@@ -1468,7 +1590,14 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 03/2019/TT-BNV Sửa đổi, bổ sung một số quy định về tuyển dụng công chức, viên chức, nâng ngạch công chức, thăng hạng chức danh n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135513) | bãi bỏ: Thông tư số 12/2023/TT-BNV bãi bỏ một số Thông tư do Bộ trưởng Bộ Nội vụ ban hành quy định về tuyển dụng công chức, viên chức, nâng ngạch cô (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=161957) | bãi bỏ: Thông tư số 01/2018/TT-BNV Hướng dẫn một số điều của Nghị định số 101/2017/NĐ-CP ngày 01 tháng 9 năm 2017 của Chính phủ về đào tạo, bồi dưỡn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127236) | sửa đổi, bổ sung: Thông tư số 04/2015/TT-BNV Sửa đổi, bổ sung Điều 6 Thông tư số 15/2012/TT-BNV ngày 25 tháng 12 năm 2012 của Bộ Nội vụ hướng dẫn về tuyển dụn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86505)</t>
+          <t>• 04/2015/TT-BNV — sửa đổi, bổ sung — hiệu lực 15/10/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86505
+• 01/2018/TT-BNV — bãi bỏ — hiệu lực 01/03/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=127236
+• 03/2019/TT-BNV — bãi bỏ — hiệu lực 01/07/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135513
+• 12/2023/TT-BNV — bãi bỏ — hiệu lực 01/10/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=161957</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
@@ -1510,7 +1639,10 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 56/2025/TT-BCT quy định về quy trình kiểm tra chuyên ngành Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=184154) | hợp nhất: Văn bản hợp nhất số 02/VBHN-BCT Thông tư quy định điều kiện, trình tự ngừng, giảm mức cung cấp điện (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158828)</t>
+          <t>• 56/2025/TT-BCT — bãi bỏ — hiệu lực 28/11/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=184154
+• 02/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158828</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
@@ -1552,7 +1684,14 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 205/2026/NĐ-CP Về cảng hàng không và bãi cất, hạ cánh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=49828ac0-6e5a-11f1-b670-d3ec94724b75) | sửa đổi, bổ sung: Nghị định số 20/2024/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 05/2021/NĐ-CP ngày 25 tháng 01 năm 2021 của Chính phủ về quản lý, k (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167258) | sửa đổi, bổ sung: Nghị định số 64/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định quy định liên quan đến hoạt động kinh doanh trong lĩnh vực hàng kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155962) | sửa đổi, bổ sung: Nghị định số 115/2024/NĐ-CP Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà đầu tư thực hiện dự án đầu tư  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170529)</t>
+          <t>• 64/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/09/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155962
+• 20/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 10/04/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167258
+• 115/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 16/09/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170529
+• 205/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=49828ac0-6e5a-11f1-b670-d3ec94724b75</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr"/>
@@ -1594,7 +1733,20 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 217/2026/NĐ-CP Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8a7d86d0-7d3f-11f1-baf6-815e332fd34f) | bãi bỏ: Nghị định số 258/2025/NĐ-CP Về quản lý công viên, cây xanh, mặt nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182758) | bãi bỏ: Nghị định số 123/2026/NĐ-CP Quy định chi tiết một số điều Luật Giao thông đường thủy nội địa và Luật sửa đổi, bổ sung một số điều của Luật G (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6d0dcf20-8cca-11f1-8008-ab19f7621b6c) | bãi bỏ: Nghị định số 207/2026/NĐ-CP Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71) | bãi bỏ: Nghị định số 241/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 165/2024/NĐ-CP ngày 26 tháng 12 năm 2024 của Chính phủ quy định ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aee9c160-8bc1-11f1-a232-057125fe017c) | bãi bỏ: Nghị định số 35/2026/NĐ-CP Quy định chi tiết một số điều của Nghị quyết về phân loại đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907) | sửa đổi, bổ sung: Nghị định số 54/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định trong lĩnh vực nhà ở, kinh doanh bất động sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186852)</t>
+          <t>• 258/2025/NĐ-CP — bãi bỏ — hiệu lực 09/10/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182758
+• 35/2026/NĐ-CP — bãi bỏ — hiệu lực 22/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907
+• 54/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 09/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186852
+• 123/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6d0dcf20-8cca-11f1-8008-ab19f7621b6c
+• 207/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71
+• 217/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8a7d86d0-7d3f-11f1-baf6-815e332fd34f
+• 241/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aee9c160-8bc1-11f1-a232-057125fe017c</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
@@ -1636,7 +1788,8 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Thông tư số 22/2015/TT-BGTVT Hướng dẫn thực hiện công tác thi đua, khen thưởng ngành Giao thông vận tải (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67935)</t>
+          <t>• 22/2015/TT-BGTVT — thay thế — hiệu lực 20/07/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67935</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
@@ -1678,7 +1831,28 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 100/2018/NĐ-CP Sửa đổi, bổ sung, bãi bỏ một số quy định về điều kiện đầu tư kinh doanh thuộc các lĩnh vực quản lý nhà n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011) | bãi bỏ: Nghị định số 96/2024/NĐ-CP Quy định chi tiết một số điều của Luật Kinh doanh bất động sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708) | bãi bỏ: Nghị định số 207/2026/NĐ-CP Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71) | bãi bỏ: Nghị định số 35/2026/NĐ-CP Quy định chi tiết một số điều của Nghị quyết về phân loại đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907) | hợp nhất: Văn bản hợp nhất số 15/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924) | hợp nhất: Văn bản hợp nhất số 03/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171) | hợp nhất: Văn bản hợp nhất số 04/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791) | sửa đổi, bổ sung: Nghị định số 31/2021/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720) | sửa đổi, bổ sung: Nghị định số 35/2023/NĐ-CP sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908)</t>
+          <t>• 100/2018/NĐ-CP — bãi bỏ — hiệu lực 15/09/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011
+• 31/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 26/03/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720
+• 35/2023/NĐ-CP — sửa đổi, bổ sung — hiệu lực 20/06/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908
+• 96/2024/NĐ-CP — bãi bỏ — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708
+• 35/2026/NĐ-CP — bãi bỏ — hiệu lực 22/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907
+• 207/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71
+• 03/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736
+• 04/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171
+• 15/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr"/>
@@ -1720,7 +1894,12 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 2168 /VBHN-BVHTTDL Quy định chi tiết một số điều của Luật sửa đổi, bổ sung một số điều của Luật Thể dục, thể thao (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168599) | sửa đổi, bổ sung: Nghị định số 31/2024/NĐ-CP sửa đổi, bổ sung một số điều của Nghị định số 01/2012/NĐ-CP, Nghị định số 61/2016/NĐ-CP và Nghị định số 36/2019/N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166544) | thay thế: Nghị định số 349/2025/NĐ-CP Quy định chế độ, chính sách đối với thành viên đội thể thao tham gia tập trung tập huấn, thi đấu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185777)</t>
+          <t>• 31/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/03/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166544
+• 349/2025/NĐ-CP — thay thế — hiệu lực 15/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185777
+• Văn bản hợp nhất số 2168 /VBHN-BVHTTDL Quy định chi tiết một số điều của Luật sửa đổi, bổ  — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168599</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr"/>
@@ -1762,7 +1941,12 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư 20/2026/TT-BTC Quy định chi tiết một số điều của Luật Thuế thu nhập doanh nghiệp và Nghị định số 320/2025/NĐ-CP ngày 15 tháng 12 nă (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6fb7dd80-59a6-11f1-a013-532655e6581a) | bãi bỏ: Nghị định số 18/2021/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 134/2016/NĐ-CP ngày 01 tháng 9 năm 2016 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151157) | sửa đổi, bổ sung: Thông tư số 81/2018/TT-BTC Sửa đổi, bổ sung Thông tư số 83/2016/TT-BTC ngày 17/6/2016 của Bộ Tài chính hướng dẫn thực hiện ưu đãi đầu tư the (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135988)</t>
+          <t>• 81/2018/TT-BTC — sửa đổi, bổ sung — hiệu lực 12/10/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135988
+• 18/2021/NĐ-CP — bãi bỏ — hiệu lực 25/04/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=151157
+• Thông tư 20/2026/TT-BTC Quy định chi tiết một số điều của Luật Thuế thu nhập doanh nghiệp  — bãi bỏ — hiệu lực 10/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=6fb7dd80-59a6-11f1-a013-532655e6581a</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr"/>
@@ -1804,7 +1988,18 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 40/2026/NĐ-CP Quy định chi tiết một số điều của Luật Thủy lợi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a0526ee0-791f-11f1-a7d3-6f8ab17b527d) | bãi bỏ: Nghị định số 32/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định trong lĩnh vực chăn nuôi và thú y (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aaff53a0-767f-11f1-a26c-15d47590a02f) | bãi bỏ: Nghị định số 39/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187831) | bãi bỏ: Nghị định số 23/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định trong lĩnh vực tài nguyên nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186456) | bãi bỏ: Nghị định số 48/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432) | thay thế: Nghị định số 43/2026/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định trong lĩnh vực bảo tồn thiên nhiên và đa dạng sinh học (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186739)</t>
+          <t>• 23/2026/NĐ-CP — bãi bỏ — hiệu lực 17/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186456
+• 32/2026/NĐ-CP — bãi bỏ — hiệu lực 21/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aaff53a0-767f-11f1-a26c-15d47590a02f
+• 39/2026/NĐ-CP — bãi bỏ — hiệu lực 25/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187831
+• 40/2026/NĐ-CP — bãi bỏ — hiệu lực 25/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a0526ee0-791f-11f1-a7d3-6f8ab17b527d
+• 43/2026/NĐ-CP — thay thế — hiệu lực 26/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186739
+• 48/2026/NĐ-CP — bãi bỏ — hiệu lực 29/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
@@ -1846,7 +2041,8 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Nghị định số 33/CP Về quản lý Nhà nước đối với hoạt động xuất khẩu, nhập khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=10351)</t>
+          <t>• 33/CP — thay thế — hiệu lực 19/04/1994
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=10351</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr"/>
@@ -1888,7 +2084,8 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 15/2018/TT-BTC Quy định về chi phí phát hành, hoán đểi, mua lại, thanh toán gốc, lãi trái phiếu Chính phủ, trái phiếu đuọc Chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128189)</t>
+          <t>• 15/2018/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/04/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=128189</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr"/>
@@ -1930,7 +2127,28 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 100/2018/NĐ-CP Sửa đổi, bổ sung, bãi bỏ một số quy định về điều kiện đầu tư kinh doanh thuộc các lĩnh vực quản lý nhà n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011) | bãi bỏ: Nghị định số 96/2024/NĐ-CP Quy định chi tiết một số điều của Luật Kinh doanh bất động sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708) | bãi bỏ: Nghị định số 207/2026/NĐ-CP Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình x (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71) | bãi bỏ: Nghị định số 35/2026/NĐ-CP Quy định chi tiết một số điều của Nghị quyết về phân loại đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907) | hợp nhất: Văn bản hợp nhất số 15/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924) | hợp nhất: Văn bản hợp nhất số 03/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170) | hợp nhất: Văn bản hợp nhất số 07/VBHN-BXD NGhị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171) | hợp nhất: Văn bản hợp nhất số 04/VBHN-BXD Nghị định về quản lý đầu tư phát triển đô thị (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791) | sửa đổi, bổ sung: Nghị định số 31/2021/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720) | sửa đổi, bổ sung: Nghị định số 35/2023/NĐ-CP sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908)</t>
+          <t>• 100/2018/NĐ-CP — bãi bỏ — hiệu lực 15/09/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=130011
+• 31/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 26/03/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147720
+• 35/2023/NĐ-CP — sửa đổi, bổ sung — hiệu lực 20/06/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160908
+• 96/2024/NĐ-CP — bãi bỏ — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169708
+• 35/2026/NĐ-CP — bãi bỏ — hiệu lực 22/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186907
+• 207/2026/NĐ-CP — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4911dc0-6e5b-11f1-b871-73e465f01c71
+• 03/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=160736
+• 04/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171791
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131170
+• 07/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131171
+• 15/VBHN-BXD — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162924</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr"/>
@@ -1972,7 +2190,8 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 74/2022/TT-BTC Quy định về hình thức, thời hạn thu, nộp, kê khai các khoản phí, lệ phí thuộc thẩm quyền quy định của Bộ Tài chín (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158215)</t>
+          <t>• 74/2022/TT-BTC — bãi bỏ — hiệu lực 22/12/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158215</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr"/>
@@ -2014,7 +2233,22 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 92/2023/NĐ-CP Bãi bỏ một số văn bản quy phạm pháp luật của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308) | hợp nhất: Văn bản hợp nhất số 951/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587) | hợp nhất: Văn bản hợp nhất số 275/VBHN-BTP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653) | sửa đổi, bổ sung: Nghị định số 24/2019/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 19/2011/NĐ-CP ngày 21 tháng 3 năm 2011 của Chính phủ quy định chi t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536) | sửa đổi, bổ sung: Nghị định số 18/2026/NĐ-CP Sửa đổi, bổ sung một số nghị định để cắt giảm, đơn giản hóa thủ tục hành chính, điều kiện kinh doanh thuộc phạm v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582) | sửa đổi, bổ sung: Nghị định số 06/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313) | sửa đổi, bổ sung: Nghị định số 114/2016/NĐ-CP Quy định lệ phí đăng ký nuôi con nuôi, lệ phí cấp giấy phép hoạt động của tổ chức con nuôi nước ngoài (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 114/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112160
+• 24/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 25/04/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134536
+• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 92/2023/NĐ-CP — bãi bỏ — hiệu lực 19/12/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=164308
+• 06/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 08/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174313
+• 18/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187582
+• 275/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174653
+• 951/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=134587</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr"/>
@@ -2056,7 +2290,10 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 36/2018/TT-BYT Quy định về Thực hành tốt bảo quản thuốc, nguyên liệu làm thuốc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135494) | bãi bỏ: Thông tư số 16/2011/TT-BYT Quy định nguyên tắc sản xuất thuốc từ dược liệu và lộ trình áp dụng nguyên tắc, tiêu chuẩn Thực hành tốt sản xuất (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26548) | thay thế: Thông tư số 36/2018/TT-BYT Quy định về Thực hành tốt bảo quản thuốc, nguyên liệu làm thuốc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135494)</t>
+          <t>• 16/2011/TT-BYT — bãi bỏ — hiệu lực 08/06/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26548
+• 36/2018/TT-BYT — bãi bỏ, thay thế — hiệu lực 10/01/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135494</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr"/>
@@ -2098,7 +2335,10 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 07/2021/TT-BVHTTDL quy định về tập huấn chuyên môn thể thao đối với người hướng dẫn tập luyện thể thao. (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149703) | bãi bỏ: Thông tư số 21/2025/TT-BVHTTDL sửa đổi, bổ sung một số điều của các Thông tư có quy định thủ tục hành chính liên quan đến hoạt động sản xuất (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186002)</t>
+          <t>• 07/2021/TT-BVHTTDL — bãi bỏ — hiệu lực 01/12/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=149703
+• 21/2025/TT-BVHTTDL — bãi bỏ — hiệu lực 26/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186002</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr"/>
@@ -2140,7 +2380,10 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 42/2024/NĐ-CP Về hoạt động lấn biển (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167334) | sửa đổi, bổ sung: Nghị định số 104/2022/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định liên quan đến việc nộp, xuất trình sổ hộ khẩu, sổ tạm trú giấy kh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220)</t>
+          <t>• 104/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167220
+• 42/2024/NĐ-CP — sửa đổi, bổ sung — hiệu lực 16/04/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=167334</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr"/>
@@ -2182,7 +2425,14 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Quyết định số 763/QĐ-UBND Bãi bỏ các Quyết định quy phạm pháp luật của Ủy ban nhân dân tỉnh Tuyên Quang và tỉnh Hà Giang trước sắp xếp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182482) | sửa đổi, bổ sung: Nghị quyết số 15/2026/NQ-HĐND Phân định cụ thể các nhiệm vụ chi về bảo vệ môi trường, ứng phó với biến đổi khí hậu của ngân sách địa phương  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=cf687d00-64ac-11f1-b68a-cdb6a707fd95) | sửa đổi, bổ sung: Nghị định số 05/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=176645) | sửa đổi, bổ sung: Nghị định số 48/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432)</t>
+          <t>• 05/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 06/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=176645
+• 763/QĐ-UBND — bãi bỏ — hiệu lực 29/09/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=182482
+• 48/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 29/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187432
+• 15/2026/NQ-HĐND — sửa đổi, bổ sung — hiệu lực 01/06/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=cf687d00-64ac-11f1-b68a-cdb6a707fd95</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr"/>
@@ -2224,7 +2474,24 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 180/2025/NĐ-CP Về cơ chế, chính sách hợp tác công tư trong lĩnh vực phát triển khoa học, công nghệ, đổi mới sáng tạo và chuyền  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187372) | bãi bỏ: Nghị định số 254/2025/NĐ-CP Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186711) | bãi bỏ: Nghị định số 291/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 103/2024/NĐ-CP ngày 30 tháng 7 năm 2024 của Chính phủ quy định về  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187822) | bãi bỏ: Nghị định số 358/2025/NĐ-CP Quy định cơ chế quản lý, tổ chức thực hiện các chương trình mục tiêu quốc gia (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=20e66500-6892-11f1-b351-6f15c9710a1a) | bãi bỏ: Nghị định 128/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 85/2024/NĐ-CP ngày 10 tháng 7 năm 2024 của Chính phủ quy định chi tiế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=cf007110-59a3-11f1-8c15-2dbf1042f751) | bãi bỏ: Nghị định số 186/2025/NĐ-CP Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179898) | bãi bỏ: Nghị định số 286/2025/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định trong lĩnh vực quản lý, sử dụng tài sản công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187799) | bãi bỏ: Nghị định số 243/2025/NĐ-CP Quy định chi tiết một số điều của Luật Đầu tư theo phương thức đối tác công tư (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9b8adda0-7e62-11f1-9c26-91051af51cab) | bãi bỏ: Nghị định 52/2026/NĐ-CP Quy định việc quản lý, sử dụng tài sản tại cơ quan Đảng Cộng sản Việt Nam (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a685c7c0-5b07-11f1-bf60-7f843e61ac43)</t>
+          <t>• 180/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187372
+• 186/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179898
+• 243/2025/NĐ-CP — bãi bỏ — hiệu lực 11/09/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9b8adda0-7e62-11f1-9c26-91051af51cab
+• 254/2025/NĐ-CP — bãi bỏ — hiệu lực 26/09/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186711
+• 286/2025/NĐ-CP — bãi bỏ — hiệu lực 03/11/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187799
+• 291/2025/NĐ-CP — bãi bỏ — hiệu lực 06/11/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187822
+• 358/2025/NĐ-CP — bãi bỏ — hiệu lực 31/12/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=20e66500-6892-11f1-b351-6f15c9710a1a
+• Nghị định 52/2026/NĐ-CP Quy định việc quản lý, sử dụng tài sản tại cơ quan Đảng Cộng sản V — bãi bỏ — hiệu lực 02/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a685c7c0-5b07-11f1-bf60-7f843e61ac43
+• Nghị định 128/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 85/2024/NĐ-CP ngày  — bãi bỏ — hiệu lực 06/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=cf007110-59a3-11f1-8c15-2dbf1042f751</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr"/>
@@ -2266,7 +2533,100 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 34/2026/TT-BCT Quy định về quản lý chất lượng sản phẩm, hàng hóa thuộc trách nhiệm quản lý nhà nước của Bộ Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c07c6060-7ab2-11f1-9a13-eb79261d7dc9) | bãi bỏ: Thông tư số 53 /2025/TT-BCT Quy định về đào tạo, cấp chứng chỉ quản lý năng lượng và kiểm toán viên năng lượng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183763) | bãi bỏ: Thông tư số 53/2025/TT-BCT Quy định về đào tạo, cấp chứng chỉ quản lý năng lượng và kiểm toán viên năng lượng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=74ca1cf0-6957-11f1-a2f2-2fc4509fa331) | bãi bỏ: Thông tư số 01/2026/TT-BCT Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Hóa chất và Nghị định số 26/2026/NĐ-CP của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186541) | bãi bỏ: Thông tư số 63/2025/TT-BCT Quy định về việc tổ chức bình chọn sản phẩm công nghiệp nông thôn tiêu biểu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186198) | hợp nhất: Văn bản hợp nhất số 45/VBHN-BCT Thông tư quy định chi tiết một số điều của Nghị định số 40/2018/NĐ-CP ngày 12 tháng 03 năm 2018 của Chính ph (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183105) | hợp nhất: Văn bản hợp nhất số 34/VBHN-BCT Thông tư sửa đổi, bổ sung một số điều của Thông tư số 57/2018/TT-BCT ngày 26/12/2018 của Bộ trưởng Bộ Công T (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4ba0520-5a68-11f1-8928-375cc07f1673) | hợp nhất: Văn bản hợp nhất số 29/VBHN-BCT Thông tư Quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179760) | hợp nhất: Văn bản hợp nhất số 46/VBHN-BCT Thông tư quy định về việc tổ chức bình chọn sản phẩm công nghiệp nông thôn tiêu biểu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183106) | hợp nhất: Văn bản hợp nhất số 43/VBHN-BCT Thông tư quy định về đào tạo, cấp chứng chỉ quản lý năng lượng và kiểm toán viên năng lượng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183103) | hợp nhất: Văn bản hợp nhất số 42/VBHN-BCT Thông tư quy định về quản lý hoạt động thương mại điện tử qua ứng dụng trên thiết bị di động (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a1949f80-688f-11f1-86d3-03b574f4bb73) | hợp nhất: Văn bản hợp nhất số 44/VBHN-BCT Thông tư quy định quản lý chất lượng sản phẩm, hàng hóa thuộc trách nhiệm quản lý của Bộ Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183104) | hợp nhất: Văn bản hợp nhất số 50/VBHN-BCT Thông tư quy định về xuất khẩu hàng dệt may sang Mê-hi-cô theo Hiệp định Đối tác Toàn diện và Tiến bộ xuyên  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183109) | hợp nhất: Văn bản hợp nhất số 39/VBHN-BCT Thông tư sửa đổi, bổ sung một số quy định về phân cấp thực hiện thủ tục hành chính trong các lĩnh vực thuộc  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=64cb0410-5b4a-11f1-b7cc-65c5b99b61dd) | hợp nhất: Văn bản hợp nhất số 05/VBHN-BCT Thông tư sửa đổi, bổ sung một số quy định về phân cấp thực hiện thủ tục hành chính trong các lĩnh vực thuộc  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186639) | hợp nhất: Văn bản hợp nhất số 47/VBHN-BCT Thông tư quy định biểu mẫu thực hiện Nghị định số 07/2016/NĐ-CP ngày 25 tháng 01 năm 2016 của Chính phủ quy  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183107) | hợp nhất: Văn bản hợp nhất số 49/VBHN-BCT Thông tư quy định dán nhãn năng lượng cho các phương tiện, thiết bị sử dụng năng lượng thuộc phạm vi quản lý (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183108) | hợp nhất: Văn bản hợp nhất số 41/VBHN-BCT Thông tư quy định về quản lý website thương mại điện tử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5aff0330-688f-11f1-8729-87811117236f) | hợp nhất: Văn bản hợp nhất số 22/VBHN-BCT Thông tư quy định chi tiết một số điều của Nghị định số 40/2018/NĐ-CP ngày 12 tháng 3 năm 2018 của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7078380-7f6e-11f1-b915-cb82e46f4076) | hợp nhất: Văn bản hợp nhất số 70/2026/VBHN-TT-BCT Thông tư quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7e65af0-926b-11f1-a5a9-cb03c709c8ec) | hợp nhất: Văn bản hợp nhất số 35/VBHN-BCT Thông tư quy định chi tiết một số điều của các Nghị định liên quan đến kinh doanh thuốc lá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86afa540-5a69-11f1-b703-9b01fda9aa7d) | hợp nhất: Văn bản hợp nhất số 24/VBHN-BCT Thông tư Quy định về xây dựng và nội dung các tài liệu quản lý an toàn trong hoạt động dầu khí (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179755) | hợp nhất: Văn bản hợp nhất số 23/VBHN-BCT Thông tư Quy định về bảo vệ công trình điện lực và an toàn trong lĩnh vực điện lực (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179753) | hợp nhất: Văn bản hợp nhất số 28/VBHN-BCT quy định chi tiết việc đăng ký quyền xuất khẩu, quyền nhập khẩu của thương nhân nước ngoài không có hiện diệ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179630) | hợp nhất: Văn bản hợp nhất số 43/VBHN-BCT Thông tư quy định về quá cảnh hàng hóa của nước Cộng hòa Nhân dân Trung Hoa qua lãnh thổ nước Cộng hòa xã hộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=2cb40290-6890-11f1-b533-cd143c3e1a65) | hợp nhất: Văn bản hợp nhất số 55/VBHN-BCT Thông tư quy định chế độ báo cáo định kỳ về cụm công nghiệp, cơ sở dữ liệu cụm công nghiệp cả nước và một số (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183114) | hợp nhất: Văn bản hợp nhất số 09/VBHN-BCT Thông tư quy định về quản lý website thương mại điện tử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186804) | hợp nhất: Văn bản hợp nhất số 08/VBHN-BCT Thông tư quy định về quản lý hoạt động thương mại điện tử qua ứng dụng trên thiết bị di động (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186803) | hợp nhất: Văn bản hợp nhất số 20/VBHN-BCT Thông tư sửa đổi, bổ sung một số quy định về phân cấp thực hiện thủ tục hành chính trong các lĩnh vực thuộc  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=1110a670-7f6e-11f1-898f-db275747e318) | hợp nhất: Văn bản hợp nhất số 53/VBHN-BCT Thông tư quy định điều kiện, trình tự thủ tục chỉ định cơ sở kiểm nghiệm kiểm chứng về an toàn thực phẩm thu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183112) | hợp nhất: Văn bản hợp nhất số 51/VBHN-BCT Thông tư quy định chi tiết một số điều của các Nghị định liên quan đến kinh doanh thuốc lá (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183110) | hợp nhất: Văn bản hợp nhất số 23/VBHN-BCT Thông tư quy định biểu mẫu thực hiện Nghị định số 07/2016/NĐ-CP ngày 25 tháng 01 năm 2016 của Chính phủ quy  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=56fe9ba0-7f6f-11f1-abea-19f66f8fba5a) | hợp nhất: Văn bản hợp nhất số 41/VBHN-BCT Thông tư xác nhận hạn ngạch thuế quan đối với mật ong tự nhiên xuất khẩu sang Nhật Bản theo Hiệp định giữa n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=181990) | hợp nhất: Văn bản hợp nhất số 52/VBHN-BCT Thông tư quy định về quản lý an toàn thực phẩm thuộc trách nhiệm của Bộ Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183111) | hợp nhất: Văn bản hợp nhất số 46/VBHN-BCT Thông tư sửa đổi, bổ sung một số điều của Thông tư số 27/2014/TT-BCT ngày 04/9/2014 của Bộ trưởng Bộ Công Th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=ca2aadd0-6890-11f1-ad29-85d5661157d0) | hợp nhất: Văn bản hợp nhất số 44/VBHN-BCT Thông tư quy định về quá cảnh hàng hóa của nước Cộng hòa xã hội dân chủ nhân dân Lào qua lãnh thổ nước Cộng  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5edac150-6890-11f1-bc6e-27aa271d77b1) | hợp nhất: Văn bản hợp nhất số 37/VBHN-BCT Thông tư quy định về quản lý, sử dụng vật liệu nổ công nghiệp, tiền chất thuốc nổ thuộc thẩm quyền quản lý c (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9e02c190-5a6a-11f1-82a6-1f2e328ebbed) | hợp nhất: Văn bản hợp nhất số 43/VBHN-BCT Thông tư quy định về quá cảnh hàng hóa của nước Cộng hòa Nhân dân Trung Hoa qua lãnh thổ nước Cộng hòa xã hộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84a3fb80-7f70-11f1-bd0f-670a645e2d65) | hợp nhất: Văn bản hợp nhất số 45/VBHN-BCT Thông tư quy định về quá cảnh hàng hóa của Vương quốc Campuchia qua lãnh thổ nước Cộng hòa xã hội chủ nghĩa  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8ef29d40-6890-11f1-8dd6-5334e80dd032) | hợp nhất: Văn bản hợp nhất số 21/VBHN-BCT Thông tư Quy định về quản lý, sử dụng vật liệu nổ công nghiệp, tiền chất thuốc nổ thuộc thẩm quyền quản lý c (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=fdb195c0-7f6e-11f1-954a-3f4ab5d9bd86) | hợp nhất: Văn bản hợp nhất số 30/VBHN-BCT Quy định thủ tục đăng ký dấu nghiệp vụ của thương nhân kinh doanh dịch vụ giám định thương mại (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179745) | hợp nhất: Văn bản hợp nhất số 47/VBHN-BCT Thông tư quy định chi tiết một số điều của Luật Quản lý ngoại thương và Nghị định số 69/2018/NĐ-CP ngày 15 t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14214f70-6891-11f1-801e-4db6a607ef12) | hợp nhất: Văn bản hợp nhất số 27/VBHN-BCT Thông tư Quy định cụ thể và hướng dẫn thi hành một số điều của Luật Hóa chất và Nghị định số 113/2017/NĐ-CP  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179764) | hợp nhất: Văn bản hợp nhất số 25/VBHN-BCT Thông tư quy định nhập khẩu thuốc lá điếu, xì gà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bbc98680-7f6f-11f1-a6c1-09d2b7111661) | hợp nhất: Văn bản hợp nhất số 26/VBHN-BCT Thông tư Quy định về quản lý, sử dụng vật liệu nổ công nghiệp, tiền chất thuốc nổ thẩm quyền quản lý của Bộ  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179763) | sửa đổi, bổ sung: Thông tư 26/2026/TT-BCT Sửa đổi, bổ sung một số quy định về phân cấp, cắt giảm, đơn giản hóa thủ tục hành chính trong các lĩnh vực thuộc phạ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c38d4c80-5819-11f1-8cfa-090ca3b5a55f) | sửa đổi, bổ sung: Thông tư số 15/2026/TT-BCT sửa đổi, bổ sung một số điều của Thông tư số 38/2025/TT-BCT của Bộ trưởng Bộ Công Thương sửa đổi, bổ sung một số  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187566)</t>
+          <t>• 53/2025/TT-BCT — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=74ca1cf0-6957-11f1-a2f2-2fc4509fa331
+• Thông tư số 53 /2025/TT-BCT Quy định về đào tạo, cấp chứng chỉ quản lý năng lượng và kiểm  — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183763
+• 01/2026/TT-BCT — bãi bỏ — hiệu lực 17/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186541
+• 63/2025/TT-BCT — bãi bỏ — hiệu lực 10/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186198
+• 15/2026/TT-BCT — sửa đổi, bổ sung — hiệu lực 10/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187566
+• Thông tư 26/2026/TT-BCT Sửa đổi, bổ sung một số quy định về phân cấp, cắt giảm, đơn giản h — sửa đổi, bổ sung — hiệu lực 29/05/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c38d4c80-5819-11f1-8cfa-090ca3b5a55f
+• 34/2026/TT-BCT — bãi bỏ — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c07c6060-7ab2-11f1-9a13-eb79261d7dc9
+• 05/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186639
+• 08/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186803
+• 09/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186804
+• 20/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=1110a670-7f6e-11f1-898f-db275747e318
+• 21/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=fdb195c0-7f6e-11f1-954a-3f4ab5d9bd86
+• 22/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7078380-7f6e-11f1-b915-cb82e46f4076
+• 23/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179753
+• 23/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=56fe9ba0-7f6f-11f1-abea-19f66f8fba5a
+• 24/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179755
+• 25/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=bbc98680-7f6f-11f1-a6c1-09d2b7111661
+• 26/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179763
+• 27/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179764
+• 28/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179630
+• 29/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179760
+• 30/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179745
+• 34/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=c4ba0520-5a68-11f1-8928-375cc07f1673
+• 35/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=86afa540-5a69-11f1-b703-9b01fda9aa7d
+• 37/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=9e02c190-5a6a-11f1-82a6-1f2e328ebbed
+• 39/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=64cb0410-5b4a-11f1-b7cc-65c5b99b61dd
+• 41/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=181990
+• 41/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5aff0330-688f-11f1-8729-87811117236f
+• 42/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=a1949f80-688f-11f1-86d3-03b574f4bb73
+• 43/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183103
+• 43/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=2cb40290-6890-11f1-b533-cd143c3e1a65
+• 43/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84a3fb80-7f70-11f1-bd0f-670a645e2d65
+• 44/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183104
+• 44/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5edac150-6890-11f1-bc6e-27aa271d77b1
+• 45/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183105
+• 45/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=8ef29d40-6890-11f1-8dd6-5334e80dd032
+• 46/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183106
+• 46/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=ca2aadd0-6890-11f1-ad29-85d5661157d0
+• 47/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14214f70-6891-11f1-801e-4db6a607ef12
+• 47/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183107
+• 49/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183108
+• 50/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183109
+• 51/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183110
+• 52/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183111
+• 53/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183112
+• 55/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183114
+• 70/2026/VBHN-TT-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=d7e65af0-926b-11f1-a5a9-cb03c709c8ec</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr"/>
@@ -2308,7 +2668,12 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 61/VBHN-VPQH hợp nhất Luật Thuế thu nhập doanh nghiệp (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4aeaa710-97ab-11f1-b15e-39b2b02f105b) | sửa đổi, bổ sung: Luật Đầu tư số 143/2025/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187601) | sửa đổi, bổ sung: Nghị định số 231/2026/NĐ-CP Quy định về quản lý, giám sát, giáo dục người chấp hành án hình sự tại cộng đồng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=386e5ad0-7d09-11f1-9c00-f9e84f25c1dc)</t>
+          <t>• 143/2025/QH15 — sửa đổi, bổ sung — hiệu lực 01/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187601
+• 231/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=386e5ad0-7d09-11f1-9c00-f9e84f25c1dc
+• 61/VBHN-VPQH — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=4aeaa710-97ab-11f1-b15e-39b2b02f105b</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr"/>
@@ -2350,7 +2715,14 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 37/2016/TT-BCT Sửa đổi, bổ sung một số điều của Thông tư số 50/2014/TT-BCT ngày 15 tháng 12 năm 2014 của Bộ trưởng Bộ Công Thươn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135507) | bãi bỏ: Thông tư số 25/2024/TT-BCT Bãi bỏ toàn bộ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Công Thương ban hành, liên tịch ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172166) | hợp nhất: Văn bản hợp nhất số 35/VBHN-BCT Quy định về quản lý nhiệm vụ khoa học và công nghệ của Bộ Công Thương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141722) | sửa đổi, bổ sung: Thông tư số 42/2019/TT-BCT Sửa đổi, bổ sung một số quy định về chế độ báo cáo định kỳ tại các Thông tư do Bộ trưởng Bộ Công Thương ban hành  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672)</t>
+          <t>• 37/2016/TT-BCT — bãi bỏ — hiệu lực 10/02/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135507
+• 42/2019/TT-BCT — sửa đổi, bổ sung — hiệu lực 05/02/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=139672
+• 25/2024/TT-BCT — bãi bỏ — hiệu lực 31/12/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172166
+• 35/VBHN-BCT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=141722</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr"/>
@@ -2392,7 +2764,18 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 01/2020/TT-BNNPTNT Quy định về chế độ báo cáo định kỳ thuộc phạm vi quản lý nhà nước của Bộ Nông nghiệp và Phát triển nông thôn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142035) | bãi bỏ: Thông tư số 06/2022/TT-BNNPTNT Sửa đổi, bổ sung một số điều của các Thông tư quy định về kiểm dịch động vật, sản phẩm động vật thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155158) | sửa đổi, bổ sung: Thông tư số 05/2025/TT-BNNMT Sửa đổi, bổ sung một số Thông tư trong lĩnh vực khai thác thuỷ sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178681) | sửa đổi, bổ sung: Thông tư số 01/2022/TT-BNNPTNT Sửa đổi, bổ sung một số Thông tư trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152678) | sửa đổi, bổ sung: Thông tư số 13/2020/TT-BNNPTNT Sửa đổi, bổ sung một số điều của Thông tư số 21/2018/TT-BNNPTNT ngày 15/11/2018 quy định ghi, nộp báo cáo, nh (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144999) | thay thế: Thông tư số 81/2025/TT-BNNMT Quy định ghi, nộp báo cáo, nhật ký khai thác thủy sản; kiểm tra tàu cá và giám sát sản lượng thủy sản tại cảng  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186332)</t>
+          <t>• 01/2020/TT-BNNPTNT — bãi bỏ — hiệu lực 05/03/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=142035
+• 13/2020/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 25/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144999
+• 01/2022/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 04/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152678
+• 06/2022/TT-BNNPTNT — bãi bỏ — hiệu lực 11/09/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155158
+• 05/2025/TT-BNNMT — sửa đổi, bổ sung — hiệu lực 18/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178681
+• 81/2025/TT-BNNMT — thay thế — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186332</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr"/>
@@ -2434,7 +2817,16 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 63/2024/TT-NHNN Quy định về hồ sơ, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hàng nước  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391) | hợp nhất: Văn bản hợp nhất số 29/VBHN-NHNN Quy định về trình tự, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138117) | hợp nhất: Văn bản hợp nhất số 10/VBHN-NHNN Quy định về trình tự, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145670) | sửa đổi, bổ sung: Thông tư số 11/2020/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 24/2017/TT-NHNN ngày 29 tháng 12 năm 2017 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144726) | sửa đổi, bổ sung: Thông tư số 14/2019/TT-NHNN Sửa đổi, bổ sung một số điều tại các Thông tư có quy định về chế độ báo cáo định kỳ của Ngân hàng Nhà nước (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583) | thay thế: Thông tư số 63/2024/TT-NHNN Quy định về hồ sơ, thủ tục thu hồi Giấy phép và thanh lý tài sản của tổ chức tín dụng, chi nhánh ngân hàng nước  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391)</t>
+          <t>• 14/2019/TT-NHNN — sửa đổi, bổ sung — hiệu lực 15/10/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=137583
+• 11/2020/TT-NHNN — sửa đổi, bổ sung — hiệu lực 17/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=144726
+• 63/2024/TT-NHNN — bãi bỏ, thay thế — hiệu lực 17/02/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174391
+• 10/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145670
+• 29/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=138117</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr"/>
@@ -2476,7 +2868,10 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 11/2017/TT-BNNPTNT Sửa đổi, bổ sung một số điều của các văn bản quy phạm pháp luật có liên quan đến chức năng, nhiệm vụ của các  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124607) | thay thế: Thông tư số 25/2017/TT-BNNPTNT Hướng dẫn quản lý chương trình, dự án, nhiệm vụ khuyến nông trung ương (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126189)</t>
+          <t>• 11/2017/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 18/07/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=124607
+• 25/2017/TT-BNNPTNT — thay thế — hiệu lực 02/01/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126189</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr"/>
@@ -2518,7 +2913,10 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>đình chỉ thi hành: Nghị định số 203/2026/NĐ-CP Quy định về thi hành án tử hình bằng tiêm thuốc độc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aac7bf60-7d02-11f1-844e-e9d0ea08e798) | sửa đổi, bổ sung: Nghị định số 184/2025/NĐ-CP Quy định phân định thẩm quyền khi tổ chức chính quyền địa phương 02 cấp và sửa đổi, bổ sung một số điều của các  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825)</t>
+          <t>• 184/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825
+• 203/2026/NĐ-CP — đình chỉ thi hành — hiệu lực 01/07/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=aac7bf60-7d02-11f1-844e-e9d0ea08e798</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr"/>
@@ -2560,7 +2958,10 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 41/2017/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định về xử phạt vi phạm hành chính trong hoạt động thủy sản; lĩnh vực t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=121985) | thay thế: Nghị định số 42/2019/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367)</t>
+          <t>• 41/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 20/05/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=121985
+• 42/2019/NĐ-CP — thay thế — hiệu lực 05/07/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr"/>
@@ -2602,7 +3003,8 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 221/2013/NĐ-CP Quy định chế độ áp dụng biện pháp xử lý hành chính đưa vào cơ sở cai nghiện bắt buộc (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32938)</t>
+          <t>• 221/2013/NĐ-CP — bãi bỏ — hiệu lực 15/02/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32938</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr"/>
@@ -2644,7 +3046,12 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 07/2024/TT-BKHCN Sửa đổi, bổ sung một số điều tại các văn bản quy phạm pháp luật thuộc thẩm quyền của Bộ trưởng Bộ Khoa học và C (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642) | sửa đổi, bổ sung: Thông tư số 13/2023/TT-BKHCN Bãi bỏ một số văn bản quy phạm pháp luật do Bộ trưởng Bộ Khoa học và Công nghệ ban hành, liên tịch ban hành (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162124) | thay thế: Thông tư số 54/2025/TT-BKHCN Quy định về hoạt động kiểm định, hiệu chuẩn, thử nghiệm phương tiện đo, chuẩn đo lường (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186195)</t>
+          <t>• 13/2023/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 30/06/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162124
+• 07/2024/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 22/11/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642
+• 54/2025/TT-BKHCN — thay thế — hiệu lực 15/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186195</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr"/>
@@ -2686,7 +3093,10 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 336/2025/NĐ-CP quy định xử phạt vi phạm hành chính trong hoạt động đường bộ. (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185666) | sửa đổi, bổ sung: Nghị định số 238/2026/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 168/2024/NĐ-CP ngày 26 tháng 12 năm 2024 của Chính phủ quy định xử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f4b0c320-79e6-11f1-8c8a-3587e086d762)</t>
+          <t>• 336/2025/NĐ-CP — bãi bỏ — hiệu lực 01/03/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185666
+• 238/2026/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/08/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f4b0c320-79e6-11f1-8c8a-3587e086d762</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr"/>
@@ -2728,7 +3138,24 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 126/2020/NĐ-CP Quy định chi tiết một số điều của Luật Quản lý thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146459) | bãi bỏ: Nghị định số 181/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347) | bãi bỏ: Nghị định số 360/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế tiêu thụ đặc biệt (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186980) | hợp nhất: Văn bản hợp nhất số 31/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225) | hợp nhất: Văn bản hợp nhất số 18/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số Điều của Luật thuế tiêu thụ đặc biệt và Luật sửa đổi, bổ sung (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118407) | hợp nhất: Văn bản hợp nhất số 16/VBHN-BTC Quy định về xử phạt vi phạm hành chính lĩnh vực về thuế và cưỡng chế thi hành quyết định hành chính thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118404) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405) | hợp nhất: Văn bản hợp nhất số 19/VBHN-BTC Quy định chi tiết thi hành một số điều của Luật quản lý thuế và Luật sửa đổi, bổ sung một số điều của Luật q (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118408) | sửa đổi, bổ sung: Nghị định số 146/2017/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 và Nghị định số 12/2015/NĐ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410)</t>
+          <t>• 146/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/02/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410
+• 126/2020/NĐ-CP — bãi bỏ — hiệu lực 05/12/2020
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=146459
+• 181/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347
+• 360/2025/NĐ-CP — bãi bỏ — hiệu lực 01/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186980
+• 16/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118404
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405
+• 18/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118407
+• 19/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118408
+• 31/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr"/>
@@ -2770,7 +3197,8 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 16/2026/TT-BXD Hướng dẫn xác định và quản lý các chi phí liên quan đến việc xây dựng, điều chỉnh chương trình, kế hoạch phát tri (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5f662d30-8e47-11f1-8158-c1fa247e8bd5)</t>
+          <t>• 16/2026/TT-BXD — sửa đổi, bổ sung — hiệu lực 29/04/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=5f662d30-8e47-11f1-8158-c1fa247e8bd5</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr"/>
@@ -2812,7 +3240,12 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị quyết số 20/2010/NQ-HĐND Về việc Quy định mức thu học phí đối với cơ sở Giáo dục mầm non, Giáo dục Phổ thông công lập từ năm học 2010-2 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51440) | sửa đổi, bổ sung: Nghị định số 74/2013/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 49/2010/NĐ-CP ngày 14 tháng 5 năm 2010 của Chính phủ quy định về mi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32559) | thay thế: Nghị định số 86/2015/NĐ-CP Quy định về cơ chế thu, quản lý học phí đối với cơ sở giáo dục thuộc hệ thống giáo dục quốc dân và chính sách miễ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84950)</t>
+          <t>• 20/2010/NQ-HĐND — sửa đổi, bổ sung — hiệu lực 19/12/2010
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51440
+• 74/2013/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/09/2013
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32559
+• 86/2015/NĐ-CP — thay thế — hiệu lực 01/12/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84950</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr"/>
@@ -2854,7 +3287,28 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 31/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405) | hợp nhất: Văn bản hợp nhất số 13/VBHN-BTC Quy định chi tiết và hướng dẫn thi hành một số điều Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67827) | sửa đổi, bổ sung: Nghị định số 91/2014/NĐ-CP Sửa đổi, bổ sung một số điều tại các Nghị định quy định về thuế (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37143) | sửa đổi, bổ sung: Nghị định số 100/2016/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật sửa đổi, bổ sung một số điều của Luật thuế giá trị  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112489) | sửa đổi, bổ sung: Nghị định số 49/2022/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 209/2013/NĐ-CP ngày 18 tháng 12 năm 2013 của Chính phủ quy định chi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155137) | sửa đổi, bổ sung: Nghị định số 146/2017/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 và Nghị định số 12/2015/NĐ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410) | sửa đổi, bổ sung: Nghị định số 12/2015/NĐ-CP Quy định chi tiết thi hành Luật sửa đổi, bổ sung một số điều của các Luật về thuế và sửa đổi, bổ sung một số điều (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51578) | sửa đổi, bổ sung: Thông tư số 130/2016/TT-BTC Hướng dẫn thực hiện Nghị định số 100/2016/NĐ-CP ngày 01 tháng 7 năm 2016 của Chính phủ quy định chi tiết thi hàn (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118086) | sửa đổi, bổ sung: Nghị định số 10/2017/NĐ-CP Ban hành Quy chế quản lý tài chính của Tập đoàn Điện lực Việt Nam và sửa đổi, bổ sung khoản 4 Điều 4 Nghị định số (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119077) | thay thế: Nghị định số 181/2025/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Thuế giá trị gia tăng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347)</t>
+          <t>• 91/2014/NĐ-CP — sửa đổi, bổ sung — hiệu lực 15/11/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=37143
+• 12/2015/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=51578
+• 100/2016/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=112489
+• 130/2016/TT-BTC — sửa đổi, bổ sung — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118086
+• 10/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/04/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119077
+• 146/2017/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/02/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=126410
+• 49/2022/NĐ-CP — sửa đổi, bổ sung — hiệu lực 12/09/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=155137
+• 181/2025/NĐ-CP — thay thế — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=187347
+• 13/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67827
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118405
+• 31/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=158225</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr"/>
@@ -2938,7 +3392,10 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Luật Đất đai số 45/2013/QH13 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32833) | thay thế: Luật Tố tụng hành chính số 93/2015/QH13 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=96035)</t>
+          <t>• 45/2013/QH13 — bãi bỏ — hiệu lực 01/07/2014
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32833
+• 93/2015/QH13 — thay thế — hiệu lực 01/07/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=96035</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr"/>
@@ -2980,7 +3437,8 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 184/2025/NĐ-CP Quy định phân định thẩm quyền khi tổ chức chính quyền địa phương 02 cấp và sửa đổi, bổ sung một số điều của các  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825)</t>
+          <t>• 184/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179825</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr"/>
@@ -3022,7 +3480,14 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 02/VBHN-BKHCN Quy định về xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường, chất lượng sản phẩm, hàng hóa (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195) | sửa đổi, bổ sung: Nghị định số 126/2021/NĐ-CP Sửa đổi, bổ sung một số điều của các nghị định quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công ng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199) | sửa đổi, bổ sung: Nghị định số 42/2019/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367) | sửa đổi, bổ sung: Nghị định số 106/2025/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực phòng cháy, chữa cháy và cứu nạn, cứu hộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735)</t>
+          <t>• 42/2019/NĐ-CP — sửa đổi, bổ sung — hiệu lực 05/07/2019
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=135367
+• 126/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154199
+• 106/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=177735
+• 02/VBHN-BKHCN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154195</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr"/>
@@ -3064,7 +3529,16 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 40/2024/TT-BGTVT Quy định về công tác phòng, chống, khắc phục hậu quả thiên tai trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157) | sửa đổi, bổ sung: Thông tư số 25/2024/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 50/2015/TT-BGTVT ngày 23 tháng 9 năm 2015 của Bộ trưởng Bộ Giao th (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214) | sửa đổi, bổ sung: Thông tư số 43/2021/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588) | sửa đổi, bổ sung: Thông tư số 36/2020/TT-BGTVT Sửa đổi, bổ sung một số điều của các Thông tư quy định về chế độ báo cáo định kỳ trong lĩnh vực đường bộ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902) | sửa đổi, bổ sung: Thông tư số 22/2023/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 03/2019/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042)</t>
+          <t>• 36/2020/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/02/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=145902
+• 43/2021/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/03/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152588
+• 22/2023/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 15/08/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=163042
+• 25/2024/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=168214
+• 40/2024/TT-BGTVT — bãi bỏ — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174157</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr"/>
@@ -3106,7 +3580,10 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 12/2025/TT-BTP Ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186318) | hợp nhất: Văn bản hợp nhất số 4101/VBHN-BTP Ban hành, hướng dẫn sử dụng, quản lý mẫu sổ quốc tịch và mẫu giấy tờ về quốc tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169236)</t>
+          <t>• 12/2025/TT-BTP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186318
+• 4101/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=169236</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr"/>
@@ -3148,7 +3625,8 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Nghị định số 136/2006/NĐ-CP Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Khiếu nại, tố cáo và các Luật sửa đổi, bổ sung một  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14979)</t>
+          <t>• 136/2006/NĐ-CP — thay thế — hiệu lực 09/12/2006
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=14979</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr"/>
@@ -3190,7 +3668,10 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 09/2005/NĐ-CP Về việc quy định xử phạt vi phạm hành chính trong lĩnh vực giao thông đường thuỷ nội địa (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18507) | sửa đổi, bổ sung: Nghị định số 77/1998/NĐ-CP Về sửa đổi, bổ sung một số điều của Nghị định số 40/CP ngày 5/7/1996 của Chính phủ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7469)</t>
+          <t>• 77/1998/NĐ-CP — sửa đổi, bổ sung — hiệu lực 11/10/1998
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=7469
+• 09/2005/NĐ-CP — sửa đổi, bổ sung — hiệu lực 24/02/2005
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=18507</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr"/>
@@ -3232,7 +3713,14 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 09/VBHN-BTC Quy định xử phạt vi phạm hành chính trong lĩnh vực chứng khoán và thị trường chứng khoán (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156570) | hợp nhất: Văn bản hợp nhất số 17/VBHN-BTC Nghị định số 156/2020/NĐ-CP Quy định xử phạt vi phạm hành chính trong lĩnh vực chứng khoán và thị trường chứ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f69936f0-6937-11f1-a48d-29bc6b0fd706) | sửa đổi, bổ sung: Nghị định số 128/2021/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2020/NĐ-CP ngày 31 tháng 12 năm 2020 của Chính phủ quy định xử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152529) | sửa đổi, bổ sung: Nghị định số 306/2025/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 156/2020/NĐ-CP ngày 31 tháng 12 năm 2020 của Chính phủ quy định xử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186388)</t>
+          <t>• 128/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/01/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=152529
+• 306/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 09/01/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186388
+• 09/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=156570
+• 17/VBHN-BTC — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=f69936f0-6937-11f1-a48d-29bc6b0fd706</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr"/>
@@ -3274,7 +3762,12 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 61/2025/TT-NHNN Quy định về mạng lưới hoạt động của ngân hàng thương mại (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185599) | hợp nhất: Văn bản hợp nhất số 12/VBHN-NHNN Quy định về mạng lưới hoạt động của ngân hàng thương mại (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179737) | sửa đổi, bổ sung: Thông tư số 08/2025/TT-NHNN Sửa đổi, bổ sung một số điều của Thông tư số 43/2015/TT-NHNN ngày 31 tháng 12 năm 2015 của Thống đốc Ngân hàng N (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178155)</t>
+          <t>• 08/2025/TT-NHNN — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178155
+• 61/2025/TT-NHNN — bãi bỏ — hiệu lực 15/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185599
+• 12/VBHN-NHNN — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179737</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr"/>
@@ -3316,7 +3809,12 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 41/2025/TT-BXD Quy định thẩm quyền, thủ tục cấp Giấy phép vận tải biển nội địa cho tàu biển nước ngoà (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185686) | sửa đổi, bổ sung: Thông tư số 48/2018/TT-BGTVT Sửa đổi, bổ sung một số điều của Thông tư số 50/2016/TT-BGTVT ngày 30 tháng 12 năm 2016 của Bộ trưởng Bộ Giao t (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131988) | sửa đổi, bổ sung: Thông tư số 08/2022/TT-BGTVT Sửa đổi, bổ sung một số điều của các Thông tư quy định liên quan đến hoạt động kinh doanh trong lĩnh vực hàng h (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154590)</t>
+          <t>• 48/2018/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 09/11/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=131988
+• 08/2022/TT-BGTVT — sửa đổi, bổ sung — hiệu lực 16/06/2022
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=154590
+• 41/2025/TT-BXD — bãi bỏ — hiệu lực 01/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=185686</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr"/>
@@ -3358,7 +3856,10 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 137/2024/NĐ-CP Quy định về giao dịch điện tử của cơ quan nhà nước và hệ thống thông tin phục vụ giao dịch điện tử (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171147) | bãi bỏ: Nghị định số 47/2024/NĐ-CP Quy định về Danh mục Cơ sở dữ liệu quốc gia; việc xây dựng, cập nhật, duy trì, khai khác và sử dụng cơ sở dữ liệu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166966)</t>
+          <t>• 47/2024/NĐ-CP — bãi bỏ — hiệu lực 09/05/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=166966
+• 137/2024/NĐ-CP — bãi bỏ — hiệu lực 23/10/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=171147</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr"/>
@@ -3400,7 +3901,12 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 07/2024/TT-BKHCN Sửa đổi, bổ sung một số điều tại các văn bản quy phạm pháp luật thuộc thẩm quyền của Bộ trưởng Bộ Khoa học và C (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642) | sửa đổi, bổ sung: Thông tư số 11/2023/TT-BKHCN Sửa đổi, bổ sung một số điều của Thông tư số 14/2014/TT-BKHCN ngày 11 tháng 6 năm 2014 của Bộ trưởng Bộ Khoa họ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162122) | sửa đổi, bổ sung: Thông tư số 22/2025/TT-BKHCN Quy định về thu thập, cập nhật, kết nối, chia sẻ, quản lý, khai thác, sử dụng dữ liệu trên Hệ thống thông tin q (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183311)</t>
+          <t>• 11/2023/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 10/08/2023
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162122
+• 07/2024/TT-BKHCN — sửa đổi, bổ sung — hiệu lực 22/11/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170642
+• 22/2025/TT-BKHCN — sửa đổi, bổ sung — hiệu lực ? (tra trên cổng)
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=183311</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr"/>
@@ -3442,7 +3948,10 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 86/2015/NĐ-CP Quy định về cơ chế thu, quản lý học phí đối với cơ sở giáo dục thuộc hệ thống giáo dục quốc dân và chính sách miễ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84950) | bãi bỏ: Nghị định số 74/2013/NĐ-CP Sửa đổi, bổ sung một số điều của Nghị định số 49/2010/NĐ-CP ngày 14 tháng 5 năm 2010 của Chính phủ quy định về mi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32559)</t>
+          <t>• 74/2013/NĐ-CP — bãi bỏ — hiệu lực 01/09/2013
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32559
+• 86/2015/NĐ-CP — bãi bỏ — hiệu lực 01/12/2015
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=84950</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr"/>
@@ -3484,7 +3993,8 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Thông tư số 128/2013/TT-BTC Quy định về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối vớ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604) | thay thế: Thông tư số 128/2013/TT-BTC Quy định về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối vớ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604)</t>
+          <t>• 128/2013/TT-BTC — bãi bỏ, thay thế — hiệu lực 01/11/2013
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32604</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr"/>
@@ -3526,7 +4036,16 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 123/2015/NĐ-CP Quy định chi tiết một số điều và biện pháp thi hành Luật Hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92897) | bãi bỏ: Nghị định số 19/2011/NĐ-CP Quy định chi tiết thi hành một số điều của Luật Nuôi con nuôi (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222) | hợp nhất: Văn bản hợp nhất số 8013/VBHN-BTP Về đăng ký và quản lý hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32721) | hợp nhất: Văn bản hợp nhất số 8013/VBHN-BTP Về đăng ký và quản lý hộ tịch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32948) | sửa đổi, bổ sung: Nghị định số 06/2012/NĐ-CP Sửa đổi, bổ sung một số điều của các Nghị định về hộ tịch, hôn nhân và gia đình và chứng thực (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27159)</t>
+          <t>• 19/2011/NĐ-CP — bãi bỏ — hiệu lực 08/05/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222
+• 06/2012/NĐ-CP — sửa đổi, bổ sung — hiệu lực 01/04/2012
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27159
+• 123/2015/NĐ-CP — bãi bỏ — hiệu lực 01/01/2016
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=92897
+• 8013/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32721
+• 8013/VBHN-BTP — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32948</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr"/>
@@ -3568,7 +4087,12 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Luật Quy hoạch đô thị và nông thôn số 47/2024/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172548) | sửa đổi, bổ sung: Quyết định 86/2026/QĐ-UBND Quy định mức hỗ trợ đào tạo, chuyển đổi nghề (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=17ca6150-5dbc-11f1-b7b9-79cb7f2eaaeb) | sửa đổi, bổ sung: Luật Sửa đổi, bổ sung một số điều của Luật Đất đai số 31/2024/QH15, Luật Nhà ở số 27/2023/QH15, Luật Kinh doanh bất động sản số 29/2023/QH15 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170509)</t>
+          <t>• Luật Sửa đổi, bổ sung một số điều của Luật Đất đai số 31/2024/QH15, Luật Nhà ở số 27/2023/ — sửa đổi, bổ sung — hiệu lực 01/08/2024
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=170509
+• 47/2024/QH15 — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172548
+• Quyết định 86/2026/QĐ-UBND Quy định mức hỗ trợ đào tạo, chuyển đổi nghề — sửa đổi, bổ sung — hiệu lực 01/06/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=17ca6150-5dbc-11f1-b7b9-79cb7f2eaaeb</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr"/>
@@ -3610,7 +4134,8 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Nghị định số 209/2025/NĐ-CP Sửa đổi, bổ sung một số điều của 11 Nghị định của Chính phủ thuộc lĩnh vực quản lý nhà nước của Bộ Quốc phòng (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179977)</t>
+          <t>• 209/2025/NĐ-CP — sửa đổi, bổ sung — hiệu lực 21/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=179977</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr"/>
@@ -3652,7 +4177,22 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>hợp nhất: Văn bản hợp nhất số 04/VBHN-BNNPTNT hợp nhất Thông tư quy định về kiểm tra, chứng nhận an toàn thực phẩm thủy sản xuất khẩu. (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136878) | hợp nhất: Văn bản hợp nhất số 02/VBHN-BNNPTNT Quy định về kiểm tra, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159656) | hợp nhất: Văn bản hợp nhất số 32/VBHN-BNNPTNT Quy định về thẩm định, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172683) | sửa đổi, bổ sung: Thông tư số 02/2017/TT-BNNPTNT Sửa đổi, bổ sung một số điều tại thông tư số 48/2013/TT-BNNPTNT ngày 12/11/2013 quy định về kiểm tra, chứng n (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122443) | sửa đổi, bổ sung: Thông tư số 16/2018/TT-BNNPTNT sửa đổi, bổ sung một số điều của Thông tư số 48/2013/TT-BNNPTNT ngày 12/11/2013 của Bộ trưởng Bộ Nông nghiệp  (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132279) | sửa đổi, bổ sung: Thông tư số 17/2025/TT-BNNMT Quy định về phân cấp quản lý nhà nước trong lĩnh vực quản lý chất lượng nông lâm sản và thủy sản (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178667) | sửa đổi, bổ sung: Thông tư số 17/2024/TT-BNNPTNT Sửa đổi, bổ sung một số Thông tư quy định thẩm định, chứng nhận cơ sở sản xuất, kinh doanh thực phẩm nông, lâ (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172685) | thay thế: Thông tư số 80/2025/TT-BNNMT Quy định về thẩm định, chứng nhận an toàn thực phẩm thủy sản xuất khẩu (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186338)</t>
+          <t>• 02/2017/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 30/03/2017
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122443
+• 16/2018/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 13/12/2018
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=132279
+• 17/2024/TT-BNNPTNT — sửa đổi, bổ sung — hiệu lực 15/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172685
+• 17/2025/TT-BNNMT — sửa đổi, bổ sung — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178667
+• 80/2025/TT-BNNMT — thay thế — hiệu lực 02/02/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=186338
+• 02/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=159656
+• 04/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136878
+• 32/VBHN-BNNPTNT — văn bản hợp nhất, chỉ để tham khảo lời văn
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=172683</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr"/>
@@ -3694,7 +4234,10 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>bãi bỏ: Nghị định số 118/2025/NĐ-CP Về thực hiện thủ tục hành chính theo cơ chế một cửa, một cửa liên thông tại Bộ phận Một cửa và Cổng Dịch vụ công (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178283) | sửa đổi, bổ sung: Nghị định số 107/2021/NĐ-CP Sửa đổi Nghị định 61/2018/NĐ-CP về thực hiện cơ chế một cửa, một cửa liên thông trong giải quyết thủ tục hành ch (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162258)</t>
+          <t>• 107/2021/NĐ-CP — sửa đổi, bổ sung — hiệu lực 06/12/2021
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=162258
+• 118/2025/NĐ-CP — bãi bỏ — hiệu lực 01/07/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=178283</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr"/>
@@ -3736,7 +4279,8 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>thay thế: Thông tư số 72/2024/TT-BCA Quy định quy trình điều tra, giải quyết tai nạn giao thông đường bộ của Cảnh sát giao thông (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174892)</t>
+          <t>• 72/2024/TT-BCA — thay thế — hiệu lực 01/01/2025
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174892</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr"/>
@@ -3778,7 +4322,10 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Chỉ thị số 02/CT-BTC Về việc đẩy nhanh tiến độ thực hiện cải cách hành chính, hiện đại hóa ngành hải quan giai đoạn 2009-2010 (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=109907) | thay thế: Thông tư số 194/2010/TT-BTC Hướng dẫn về thủ tục hải quan; kiểm tra, giám sát hải quan; thuế xuất khẩu, thuế nhập khẩu và quản lý thuế đối v (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26032)</t>
+          <t>• 194/2010/TT-BTC — thay thế — hiệu lực 21/01/2011
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26032
+• 02/CT-BTC — sửa đổi, bổ sung — hiệu lực ? (tra trên cổng)
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=109907</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr"/>
@@ -3820,7 +4367,8 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>sửa đổi, bổ sung: Thông tư số 129/2026/TT-BTC Sửa đổi, bổ sung một số điều của Thông tư số 98/2025/TT-BTC ngày 27 tháng 10 năm 2025 của Bộ trưởng Bộ Tài chính (https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0e343320-a82e-11f1-b262-51fb030e2e1b)</t>
+          <t>• 129/2026/TT-BTC — sửa đổi, bổ sung — hiệu lực 27/08/2026
+  https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=0e343320-a82e-11f1-b262-51fb030e2e1b</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr"/>
